--- a/artfynd/A 26079-2020 artfynd.xlsx
+++ b/artfynd/A 26079-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714957</v>
+        <v>113714956</v>
       </c>
       <c r="B2" t="n">
-        <v>56029</v>
+        <v>78201</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638143</v>
+        <v>638127</v>
       </c>
       <c r="R2" t="n">
-        <v>7033756</v>
+        <v>7033780</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>En tupp</t>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113712749</v>
+        <v>113714953</v>
       </c>
       <c r="B3" t="n">
-        <v>78201</v>
+        <v>90131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638039</v>
+        <v>638082</v>
       </c>
       <c r="R3" t="n">
-        <v>7033691</v>
+        <v>7033727</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -862,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +892,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113712793</v>
+        <v>113712798</v>
       </c>
       <c r="B4" t="n">
         <v>78201</v>
@@ -937,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638229</v>
+        <v>638106</v>
       </c>
       <c r="R4" t="n">
-        <v>7033645</v>
+        <v>7033670</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1003,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113712801</v>
+        <v>113712799</v>
       </c>
       <c r="B5" t="n">
-        <v>90573</v>
+        <v>90131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638021</v>
+        <v>638079</v>
       </c>
       <c r="R5" t="n">
-        <v>7033632</v>
+        <v>7033653</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113712756</v>
+        <v>113712749</v>
       </c>
       <c r="B6" t="n">
         <v>78201</v>
@@ -1149,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638127</v>
+        <v>638039</v>
       </c>
       <c r="R6" t="n">
-        <v>7033780</v>
+        <v>7033691</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113714953</v>
+        <v>113714984</v>
       </c>
       <c r="B7" t="n">
-        <v>90131</v>
+        <v>78794</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1260,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638082</v>
+        <v>638151</v>
       </c>
       <c r="R7" t="n">
-        <v>7033727</v>
+        <v>7033618</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113714890</v>
+        <v>113712792</v>
       </c>
       <c r="B8" t="n">
-        <v>78794</v>
+        <v>90149</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1366,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637878</v>
+        <v>638281</v>
       </c>
       <c r="R8" t="n">
-        <v>7033847</v>
+        <v>7033658</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1396,12 +1391,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113712797</v>
+        <v>113712751</v>
       </c>
       <c r="B9" t="n">
-        <v>90131</v>
+        <v>56029</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,25 +1439,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1472,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638110</v>
+        <v>638206</v>
       </c>
       <c r="R9" t="n">
-        <v>7033643</v>
+        <v>7033778</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1508,6 +1503,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>En höna</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113712751</v>
+        <v>113714890</v>
       </c>
       <c r="B10" t="n">
-        <v>56029</v>
+        <v>78794</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,25 +1550,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638206</v>
+        <v>637878</v>
       </c>
       <c r="R10" t="n">
-        <v>7033778</v>
+        <v>7033847</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1608,17 +1608,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>En höna</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,7 +1644,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712752</v>
+        <v>113712757</v>
       </c>
       <c r="B11" t="n">
         <v>56029</v>
@@ -1689,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638041</v>
+        <v>638143</v>
       </c>
       <c r="R11" t="n">
-        <v>7033714</v>
+        <v>7033756</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712791</v>
+        <v>113712802</v>
       </c>
       <c r="B12" t="n">
-        <v>90518</v>
+        <v>90131</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,16 +1771,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638310</v>
+        <v>638021</v>
       </c>
       <c r="R12" t="n">
-        <v>7033687</v>
+        <v>7033637</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1831,11 +1831,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Mycket gammal fruktkropp på gammal granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,7 +1861,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113712796</v>
+        <v>113712795</v>
       </c>
       <c r="B13" t="n">
         <v>90131</v>
@@ -1906,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638130</v>
+        <v>638152</v>
       </c>
       <c r="R13" t="n">
-        <v>7033646</v>
+        <v>7033629</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1972,7 +1967,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113712755</v>
+        <v>113714955</v>
       </c>
       <c r="B14" t="n">
         <v>96367</v>
@@ -2078,7 +2073,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113714954</v>
+        <v>113712754</v>
       </c>
       <c r="B15" t="n">
         <v>90573</v>
@@ -2184,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113712795</v>
+        <v>113712793</v>
       </c>
       <c r="B16" t="n">
-        <v>90131</v>
+        <v>78201</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,21 +2195,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2224,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638152</v>
+        <v>638229</v>
       </c>
       <c r="R16" t="n">
-        <v>7033629</v>
+        <v>7033645</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2290,10 +2285,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113712792</v>
+        <v>113714952</v>
       </c>
       <c r="B17" t="n">
-        <v>90149</v>
+        <v>56029</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2302,25 +2297,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2325,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638281</v>
+        <v>638041</v>
       </c>
       <c r="R17" t="n">
-        <v>7033658</v>
+        <v>7033714</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2366,6 +2361,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113712784</v>
+        <v>113712797</v>
       </c>
       <c r="B18" t="n">
-        <v>78794</v>
+        <v>90131</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2412,21 +2412,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638151</v>
+        <v>638110</v>
       </c>
       <c r="R18" t="n">
-        <v>7033618</v>
+        <v>7033643</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2502,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113712794</v>
+        <v>113712683</v>
       </c>
       <c r="B19" t="n">
-        <v>90592</v>
+        <v>78201</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2518,21 +2518,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5467</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638195</v>
+        <v>637971</v>
       </c>
       <c r="R19" t="n">
-        <v>7033639</v>
+        <v>7033859</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2572,12 +2572,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2719,10 +2724,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113712799</v>
+        <v>113712794</v>
       </c>
       <c r="B21" t="n">
-        <v>90131</v>
+        <v>90592</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2735,21 +2740,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5467</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2759,10 +2764,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>638079</v>
+        <v>638195</v>
       </c>
       <c r="R21" t="n">
-        <v>7033653</v>
+        <v>7033639</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2825,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113712683</v>
+        <v>113712801</v>
       </c>
       <c r="B22" t="n">
-        <v>78201</v>
+        <v>90573</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2837,25 +2842,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>637971</v>
+        <v>638021</v>
       </c>
       <c r="R22" t="n">
-        <v>7033859</v>
+        <v>7033632</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2895,17 +2900,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Riklig</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2936,7 +2936,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113712802</v>
+        <v>113712796</v>
       </c>
       <c r="B23" t="n">
         <v>90131</v>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>638021</v>
+        <v>638130</v>
       </c>
       <c r="R23" t="n">
-        <v>7033637</v>
+        <v>7033646</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3042,10 +3042,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113712798</v>
+        <v>113712791</v>
       </c>
       <c r="B24" t="n">
-        <v>78201</v>
+        <v>90518</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3058,21 +3058,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3082,10 +3077,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>638106</v>
+        <v>638310</v>
       </c>
       <c r="R24" t="n">
-        <v>7033670</v>
+        <v>7033687</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3118,6 +3113,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mycket gammal fruktkropp på gammal granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 26079-2020 artfynd.xlsx
+++ b/artfynd/A 26079-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714956</v>
+        <v>113712799</v>
       </c>
       <c r="B2" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638127</v>
+        <v>638079</v>
       </c>
       <c r="R2" t="n">
-        <v>7033780</v>
+        <v>7033653</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113714953</v>
+        <v>113712754</v>
       </c>
       <c r="B3" t="n">
-        <v>90131</v>
+        <v>90577</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638082</v>
+        <v>638088</v>
       </c>
       <c r="R3" t="n">
-        <v>7033727</v>
+        <v>7033754</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113712798</v>
+        <v>113712792</v>
       </c>
       <c r="B4" t="n">
-        <v>78201</v>
+        <v>90153</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638106</v>
+        <v>638281</v>
       </c>
       <c r="R4" t="n">
-        <v>7033670</v>
+        <v>7033658</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113712799</v>
+        <v>113712794</v>
       </c>
       <c r="B5" t="n">
-        <v>90131</v>
+        <v>90596</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5467</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638079</v>
+        <v>638195</v>
       </c>
       <c r="R5" t="n">
-        <v>7033653</v>
+        <v>7033639</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113712749</v>
+        <v>113714957</v>
       </c>
       <c r="B6" t="n">
-        <v>78201</v>
+        <v>56029</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638039</v>
+        <v>638143</v>
       </c>
       <c r="R6" t="n">
-        <v>7033691</v>
+        <v>7033756</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1184,7 +1179,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Riklig</t>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113714984</v>
+        <v>113714890</v>
       </c>
       <c r="B7" t="n">
         <v>78794</v>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638151</v>
+        <v>637878</v>
       </c>
       <c r="R7" t="n">
-        <v>7033618</v>
+        <v>7033847</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1285,12 +1280,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113712792</v>
+        <v>113712751</v>
       </c>
       <c r="B8" t="n">
-        <v>90149</v>
+        <v>56029</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1328,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638281</v>
+        <v>638206</v>
       </c>
       <c r="R8" t="n">
-        <v>7033658</v>
+        <v>7033778</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,6 +1392,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En höna</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113712751</v>
+        <v>113714955</v>
       </c>
       <c r="B9" t="n">
-        <v>56029</v>
+        <v>96371</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1443,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638206</v>
+        <v>638085</v>
       </c>
       <c r="R9" t="n">
-        <v>7033778</v>
+        <v>7033772</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1503,11 +1503,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>En höna</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113714890</v>
+        <v>113712791</v>
       </c>
       <c r="B10" t="n">
-        <v>78794</v>
+        <v>90522</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,21 +1549,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Vedskivlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1578,10 +1568,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>637878</v>
+        <v>638310</v>
       </c>
       <c r="R10" t="n">
-        <v>7033847</v>
+        <v>7033687</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1608,12 +1598,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Mycket gammal fruktkropp på gammal granlåga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712757</v>
+        <v>113712801</v>
       </c>
       <c r="B11" t="n">
-        <v>56029</v>
+        <v>90577</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638143</v>
+        <v>638021</v>
       </c>
       <c r="R11" t="n">
-        <v>7033756</v>
+        <v>7033632</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1720,11 +1715,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>En tupp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712802</v>
+        <v>113712749</v>
       </c>
       <c r="B12" t="n">
-        <v>90131</v>
+        <v>78201</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,21 +1761,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1785,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638021</v>
+        <v>638039</v>
       </c>
       <c r="R12" t="n">
-        <v>7033637</v>
+        <v>7033691</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1831,6 +1821,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113712795</v>
+        <v>113714889</v>
       </c>
       <c r="B13" t="n">
-        <v>90131</v>
+        <v>78201</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,21 +1872,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638152</v>
+        <v>637971</v>
       </c>
       <c r="R13" t="n">
-        <v>7033629</v>
+        <v>7033859</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1931,12 +1926,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113714955</v>
+        <v>113712793</v>
       </c>
       <c r="B14" t="n">
-        <v>96367</v>
+        <v>78201</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,25 +1979,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638085</v>
+        <v>638229</v>
       </c>
       <c r="R14" t="n">
-        <v>7033772</v>
+        <v>7033645</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113712754</v>
+        <v>113712756</v>
       </c>
       <c r="B15" t="n">
-        <v>90573</v>
+        <v>78201</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638088</v>
+        <v>638127</v>
       </c>
       <c r="R15" t="n">
-        <v>7033754</v>
+        <v>7033780</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2149,6 +2149,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2179,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113712793</v>
+        <v>113712784</v>
       </c>
       <c r="B16" t="n">
-        <v>78201</v>
+        <v>78794</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,21 +2200,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638229</v>
+        <v>638151</v>
       </c>
       <c r="R16" t="n">
-        <v>7033645</v>
+        <v>7033618</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2285,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113714952</v>
+        <v>113712797</v>
       </c>
       <c r="B17" t="n">
-        <v>56029</v>
+        <v>90135</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2297,25 +2302,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2325,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638041</v>
+        <v>638110</v>
       </c>
       <c r="R17" t="n">
-        <v>7033714</v>
+        <v>7033643</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2361,11 +2366,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>En tupp</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113712797</v>
+        <v>113712795</v>
       </c>
       <c r="B18" t="n">
-        <v>90131</v>
+        <v>90135</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638110</v>
+        <v>638152</v>
       </c>
       <c r="R18" t="n">
-        <v>7033643</v>
+        <v>7033629</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2502,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113712683</v>
+        <v>113714952</v>
       </c>
       <c r="B19" t="n">
-        <v>78201</v>
+        <v>56029</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,25 +2514,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>637971</v>
+        <v>638041</v>
       </c>
       <c r="R19" t="n">
-        <v>7033859</v>
+        <v>7033714</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2572,17 +2572,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Riklig</t>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2613,10 +2613,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113712800</v>
+        <v>113712796</v>
       </c>
       <c r="B20" t="n">
-        <v>56810</v>
+        <v>90135</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>638031</v>
+        <v>638130</v>
       </c>
       <c r="R20" t="n">
-        <v>7033639</v>
+        <v>7033646</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2689,11 +2689,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,10 +2719,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113712794</v>
+        <v>113712802</v>
       </c>
       <c r="B21" t="n">
-        <v>90592</v>
+        <v>90135</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2740,21 +2735,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5467</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2764,10 +2759,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>638195</v>
+        <v>638021</v>
       </c>
       <c r="R21" t="n">
-        <v>7033639</v>
+        <v>7033637</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2830,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113712801</v>
+        <v>113712800</v>
       </c>
       <c r="B22" t="n">
-        <v>90573</v>
+        <v>56810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2842,25 +2837,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638021</v>
+        <v>638031</v>
       </c>
       <c r="R22" t="n">
-        <v>7033632</v>
+        <v>7033639</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2906,6 +2901,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2936,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113712796</v>
+        <v>113712798</v>
       </c>
       <c r="B23" t="n">
-        <v>90131</v>
+        <v>78201</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>638130</v>
+        <v>638106</v>
       </c>
       <c r="R23" t="n">
-        <v>7033646</v>
+        <v>7033670</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3042,10 +3042,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113712791</v>
+        <v>113714953</v>
       </c>
       <c r="B24" t="n">
-        <v>90518</v>
+        <v>90135</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3058,16 +3058,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3077,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>638310</v>
+        <v>638082</v>
       </c>
       <c r="R24" t="n">
-        <v>7033687</v>
+        <v>7033727</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3113,11 +3118,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mycket gammal fruktkropp på gammal granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 26079-2020 artfynd.xlsx
+++ b/artfynd/A 26079-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113712799</v>
+        <v>113712797</v>
       </c>
       <c r="B2" t="n">
         <v>90135</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638079</v>
+        <v>638110</v>
       </c>
       <c r="R2" t="n">
-        <v>7033653</v>
+        <v>7033643</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113712754</v>
+        <v>113712784</v>
       </c>
       <c r="B3" t="n">
-        <v>90577</v>
+        <v>78794</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638088</v>
+        <v>638151</v>
       </c>
       <c r="R3" t="n">
-        <v>7033754</v>
+        <v>7033618</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113712792</v>
+        <v>113712755</v>
       </c>
       <c r="B4" t="n">
-        <v>90153</v>
+        <v>96371</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638281</v>
+        <v>638085</v>
       </c>
       <c r="R4" t="n">
-        <v>7033658</v>
+        <v>7033772</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113712794</v>
+        <v>113712793</v>
       </c>
       <c r="B5" t="n">
-        <v>90596</v>
+        <v>78201</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5467</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638195</v>
+        <v>638229</v>
       </c>
       <c r="R5" t="n">
-        <v>7033639</v>
+        <v>7033645</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113714957</v>
+        <v>113712796</v>
       </c>
       <c r="B6" t="n">
-        <v>56029</v>
+        <v>90135</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,25 +1111,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638143</v>
+        <v>638130</v>
       </c>
       <c r="R6" t="n">
-        <v>7033756</v>
+        <v>7033646</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1175,11 +1175,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>En tupp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113714890</v>
+        <v>113712802</v>
       </c>
       <c r="B7" t="n">
-        <v>78794</v>
+        <v>90135</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637878</v>
+        <v>638021</v>
       </c>
       <c r="R7" t="n">
-        <v>7033847</v>
+        <v>7033637</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,12 +1275,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1311,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113712751</v>
+        <v>113712756</v>
       </c>
       <c r="B8" t="n">
-        <v>56029</v>
+        <v>78201</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,25 +1323,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1351,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638206</v>
+        <v>638127</v>
       </c>
       <c r="R8" t="n">
-        <v>7033778</v>
+        <v>7033780</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1396,7 +1391,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>En höna</t>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1422,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113714955</v>
+        <v>113714950</v>
       </c>
       <c r="B9" t="n">
-        <v>96371</v>
+        <v>78201</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,25 +1434,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1462,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638085</v>
+        <v>638039</v>
       </c>
       <c r="R9" t="n">
-        <v>7033772</v>
+        <v>7033691</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1503,6 +1498,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1533,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113712791</v>
+        <v>113712751</v>
       </c>
       <c r="B10" t="n">
-        <v>90522</v>
+        <v>56029</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,20 +1545,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6040186</v>
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1568,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638310</v>
+        <v>638206</v>
       </c>
       <c r="R10" t="n">
-        <v>7033687</v>
+        <v>7033778</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1608,7 +1613,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Mycket gammal fruktkropp på gammal granlåga</t>
+          <t>En höna</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712801</v>
+        <v>113712792</v>
       </c>
       <c r="B11" t="n">
-        <v>90577</v>
+        <v>90153</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1656,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638021</v>
+        <v>638281</v>
       </c>
       <c r="R11" t="n">
-        <v>7033632</v>
+        <v>7033658</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1745,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712749</v>
+        <v>113712801</v>
       </c>
       <c r="B12" t="n">
-        <v>78201</v>
+        <v>90577</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1757,25 +1762,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638039</v>
+        <v>638021</v>
       </c>
       <c r="R12" t="n">
-        <v>7033691</v>
+        <v>7033632</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1821,11 +1826,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113712793</v>
+        <v>113712753</v>
       </c>
       <c r="B14" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,21 +1983,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638229</v>
+        <v>638082</v>
       </c>
       <c r="R14" t="n">
-        <v>7033645</v>
+        <v>7033727</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113712756</v>
+        <v>113712752</v>
       </c>
       <c r="B15" t="n">
-        <v>78201</v>
+        <v>56029</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2085,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638127</v>
+        <v>638041</v>
       </c>
       <c r="R15" t="n">
-        <v>7033780</v>
+        <v>7033714</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Riklig</t>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,10 +2184,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113712784</v>
+        <v>113712798</v>
       </c>
       <c r="B16" t="n">
-        <v>78794</v>
+        <v>78201</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,21 +2200,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2224,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638151</v>
+        <v>638106</v>
       </c>
       <c r="R16" t="n">
-        <v>7033618</v>
+        <v>7033670</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2290,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113712797</v>
+        <v>113712684</v>
       </c>
       <c r="B17" t="n">
-        <v>90135</v>
+        <v>78794</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,21 +2306,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638110</v>
+        <v>637878</v>
       </c>
       <c r="R17" t="n">
-        <v>7033643</v>
+        <v>7033847</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2360,12 +2360,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,10 +2396,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113712795</v>
+        <v>113714954</v>
       </c>
       <c r="B18" t="n">
-        <v>90135</v>
+        <v>90577</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2408,25 +2408,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638152</v>
+        <v>638088</v>
       </c>
       <c r="R18" t="n">
-        <v>7033629</v>
+        <v>7033754</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113714952</v>
+        <v>113712757</v>
       </c>
       <c r="B19" t="n">
         <v>56029</v>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638041</v>
+        <v>638143</v>
       </c>
       <c r="R19" t="n">
-        <v>7033714</v>
+        <v>7033756</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113712796</v>
+        <v>113712799</v>
       </c>
       <c r="B20" t="n">
         <v>90135</v>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>638130</v>
+        <v>638079</v>
       </c>
       <c r="R20" t="n">
-        <v>7033646</v>
+        <v>7033653</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2719,7 +2719,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113712802</v>
+        <v>113712795</v>
       </c>
       <c r="B21" t="n">
         <v>90135</v>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>638021</v>
+        <v>638152</v>
       </c>
       <c r="R21" t="n">
-        <v>7033637</v>
+        <v>7033629</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2825,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113712800</v>
+        <v>113712794</v>
       </c>
       <c r="B22" t="n">
-        <v>56810</v>
+        <v>90596</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5467</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638031</v>
+        <v>638195</v>
       </c>
       <c r="R22" t="n">
         <v>7033639</v>
@@ -2901,11 +2901,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2936,10 +2931,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113712798</v>
+        <v>113712800</v>
       </c>
       <c r="B23" t="n">
-        <v>78201</v>
+        <v>56810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2952,21 +2947,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2976,10 +2971,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>638106</v>
+        <v>638031</v>
       </c>
       <c r="R23" t="n">
-        <v>7033670</v>
+        <v>7033639</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3012,6 +3007,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3042,10 +3042,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113714953</v>
+        <v>113712791</v>
       </c>
       <c r="B24" t="n">
-        <v>90135</v>
+        <v>90522</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3058,21 +3058,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3082,10 +3077,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>638082</v>
+        <v>638310</v>
       </c>
       <c r="R24" t="n">
-        <v>7033727</v>
+        <v>7033687</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3118,6 +3113,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Mycket gammal fruktkropp på gammal granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 26079-2020 artfynd.xlsx
+++ b/artfynd/A 26079-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113712797</v>
+        <v>113712755</v>
       </c>
       <c r="B2" t="n">
-        <v>90135</v>
+        <v>96371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638110</v>
+        <v>638085</v>
       </c>
       <c r="R2" t="n">
-        <v>7033643</v>
+        <v>7033772</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113712784</v>
+        <v>113712795</v>
       </c>
       <c r="B3" t="n">
-        <v>78794</v>
+        <v>90135</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638151</v>
+        <v>638152</v>
       </c>
       <c r="R3" t="n">
-        <v>7033618</v>
+        <v>7033629</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113712755</v>
+        <v>113712801</v>
       </c>
       <c r="B4" t="n">
-        <v>96371</v>
+        <v>90577</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638085</v>
+        <v>638021</v>
       </c>
       <c r="R4" t="n">
-        <v>7033772</v>
+        <v>7033632</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113712793</v>
+        <v>113712800</v>
       </c>
       <c r="B5" t="n">
-        <v>78201</v>
+        <v>56810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638229</v>
+        <v>638031</v>
       </c>
       <c r="R5" t="n">
-        <v>7033645</v>
+        <v>7033639</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1069,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,7 +1104,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113712796</v>
+        <v>113712797</v>
       </c>
       <c r="B6" t="n">
         <v>90135</v>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638130</v>
+        <v>638110</v>
       </c>
       <c r="R6" t="n">
-        <v>7033646</v>
+        <v>7033643</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113712802</v>
+        <v>113714957</v>
       </c>
       <c r="B7" t="n">
-        <v>90135</v>
+        <v>56029</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1217,25 +1222,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638021</v>
+        <v>638143</v>
       </c>
       <c r="R7" t="n">
-        <v>7033637</v>
+        <v>7033756</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1281,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1311,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113712756</v>
+        <v>113712751</v>
       </c>
       <c r="B8" t="n">
-        <v>78201</v>
+        <v>56029</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638127</v>
+        <v>638206</v>
       </c>
       <c r="R8" t="n">
-        <v>7033780</v>
+        <v>7033778</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1391,7 +1401,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Riklig</t>
+          <t>En höna</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113714950</v>
+        <v>113712796</v>
       </c>
       <c r="B9" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1438,21 +1448,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1462,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638039</v>
+        <v>638130</v>
       </c>
       <c r="R9" t="n">
-        <v>7033691</v>
+        <v>7033646</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1498,11 +1508,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1533,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113712751</v>
+        <v>113712802</v>
       </c>
       <c r="B10" t="n">
-        <v>56029</v>
+        <v>90135</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1545,25 +1550,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638206</v>
+        <v>638021</v>
       </c>
       <c r="R10" t="n">
-        <v>7033778</v>
+        <v>7033637</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1609,11 +1614,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>En höna</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1644,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712792</v>
+        <v>113714950</v>
       </c>
       <c r="B11" t="n">
-        <v>90153</v>
+        <v>78201</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1660,21 +1660,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638281</v>
+        <v>638039</v>
       </c>
       <c r="R11" t="n">
-        <v>7033658</v>
+        <v>7033691</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1720,6 +1720,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113712801</v>
+        <v>113714952</v>
       </c>
       <c r="B12" t="n">
-        <v>90577</v>
+        <v>56029</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,25 +1767,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638021</v>
+        <v>638041</v>
       </c>
       <c r="R12" t="n">
-        <v>7033632</v>
+        <v>7033714</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1826,6 +1831,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113714889</v>
+        <v>113712791</v>
       </c>
       <c r="B13" t="n">
-        <v>78201</v>
+        <v>90522</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,21 +1882,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1901,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>637971</v>
+        <v>638310</v>
       </c>
       <c r="R13" t="n">
-        <v>7033859</v>
+        <v>7033687</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1926,17 +1931,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Riklig</t>
+          <t>Mycket gammal fruktkropp på gammal granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113712753</v>
+        <v>113714954</v>
       </c>
       <c r="B14" t="n">
-        <v>90135</v>
+        <v>90577</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,25 +1984,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2007,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638082</v>
+        <v>638088</v>
       </c>
       <c r="R14" t="n">
-        <v>7033727</v>
+        <v>7033754</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2073,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113712752</v>
+        <v>113714889</v>
       </c>
       <c r="B15" t="n">
-        <v>56029</v>
+        <v>78201</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,25 +2090,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2113,10 +2118,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638041</v>
+        <v>637971</v>
       </c>
       <c r="R15" t="n">
-        <v>7033714</v>
+        <v>7033859</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2143,17 +2148,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>En tupp</t>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2184,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113712798</v>
+        <v>113712792</v>
       </c>
       <c r="B16" t="n">
-        <v>78201</v>
+        <v>90153</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2200,21 +2205,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2224,10 +2229,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638106</v>
+        <v>638281</v>
       </c>
       <c r="R16" t="n">
-        <v>7033670</v>
+        <v>7033658</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2396,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113714954</v>
+        <v>113712793</v>
       </c>
       <c r="B18" t="n">
-        <v>90577</v>
+        <v>78201</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2408,25 +2413,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2436,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638088</v>
+        <v>638229</v>
       </c>
       <c r="R18" t="n">
-        <v>7033754</v>
+        <v>7033645</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2502,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113712757</v>
+        <v>113712794</v>
       </c>
       <c r="B19" t="n">
-        <v>56029</v>
+        <v>90596</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2514,25 +2519,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>5467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638143</v>
+        <v>638195</v>
       </c>
       <c r="R19" t="n">
-        <v>7033756</v>
+        <v>7033639</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2578,11 +2583,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>En tupp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2613,10 +2613,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113712799</v>
+        <v>113712798</v>
       </c>
       <c r="B20" t="n">
-        <v>90135</v>
+        <v>78201</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>638079</v>
+        <v>638106</v>
       </c>
       <c r="R20" t="n">
-        <v>7033653</v>
+        <v>7033670</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2719,7 +2719,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113712795</v>
+        <v>113712753</v>
       </c>
       <c r="B21" t="n">
         <v>90135</v>
@@ -2759,10 +2759,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>638152</v>
+        <v>638082</v>
       </c>
       <c r="R21" t="n">
-        <v>7033629</v>
+        <v>7033727</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2825,10 +2825,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113712794</v>
+        <v>113712756</v>
       </c>
       <c r="B22" t="n">
-        <v>90596</v>
+        <v>78201</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5467</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638195</v>
+        <v>638127</v>
       </c>
       <c r="R22" t="n">
-        <v>7033639</v>
+        <v>7033780</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2901,6 +2901,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2931,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113712800</v>
+        <v>113712799</v>
       </c>
       <c r="B23" t="n">
-        <v>56810</v>
+        <v>90135</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2947,21 +2952,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2971,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>638031</v>
+        <v>638079</v>
       </c>
       <c r="R23" t="n">
-        <v>7033639</v>
+        <v>7033653</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3007,11 +3012,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3042,10 +3042,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113712791</v>
+        <v>113714984</v>
       </c>
       <c r="B24" t="n">
-        <v>90522</v>
+        <v>78794</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3058,16 +3058,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6040186</v>
+        <v>6453</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3077,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>638310</v>
+        <v>638151</v>
       </c>
       <c r="R24" t="n">
-        <v>7033687</v>
+        <v>7033618</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3113,11 +3118,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Mycket gammal fruktkropp på gammal granlåga</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 26079-2020 artfynd.xlsx
+++ b/artfynd/A 26079-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113712755</v>
+        <v>113714984</v>
       </c>
       <c r="B2" t="n">
-        <v>96371</v>
+        <v>78794</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638085</v>
+        <v>638151</v>
       </c>
       <c r="R2" t="n">
-        <v>7033772</v>
+        <v>7033618</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113712795</v>
+        <v>113714954</v>
       </c>
       <c r="B3" t="n">
-        <v>90135</v>
+        <v>90577</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638152</v>
+        <v>638088</v>
       </c>
       <c r="R3" t="n">
-        <v>7033629</v>
+        <v>7033754</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113712801</v>
+        <v>113712753</v>
       </c>
       <c r="B4" t="n">
-        <v>90577</v>
+        <v>90135</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638021</v>
+        <v>638082</v>
       </c>
       <c r="R4" t="n">
-        <v>7033632</v>
+        <v>7033727</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113712800</v>
+        <v>113714951</v>
       </c>
       <c r="B5" t="n">
-        <v>56810</v>
+        <v>56029</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1005,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638031</v>
+        <v>638206</v>
       </c>
       <c r="R5" t="n">
-        <v>7033639</v>
+        <v>7033778</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>En höna</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113712797</v>
+        <v>113712752</v>
       </c>
       <c r="B6" t="n">
-        <v>90135</v>
+        <v>56029</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1116,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638110</v>
+        <v>638041</v>
       </c>
       <c r="R6" t="n">
-        <v>7033643</v>
+        <v>7033714</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1180,6 +1180,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113714957</v>
+        <v>113712791</v>
       </c>
       <c r="B7" t="n">
-        <v>56029</v>
+        <v>90522</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1227,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638143</v>
+        <v>638310</v>
       </c>
       <c r="R7" t="n">
-        <v>7033756</v>
+        <v>7033687</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>En tupp</t>
+          <t>Mycket gammal fruktkropp på gammal granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113712751</v>
+        <v>113712801</v>
       </c>
       <c r="B8" t="n">
-        <v>56029</v>
+        <v>90577</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638206</v>
+        <v>638021</v>
       </c>
       <c r="R8" t="n">
-        <v>7033778</v>
+        <v>7033632</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,11 +1397,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>En höna</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,7 +1427,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113712796</v>
+        <v>113712799</v>
       </c>
       <c r="B9" t="n">
         <v>90135</v>
@@ -1472,10 +1467,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638130</v>
+        <v>638079</v>
       </c>
       <c r="R9" t="n">
-        <v>7033646</v>
+        <v>7033653</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1538,7 +1533,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113712802</v>
+        <v>113712796</v>
       </c>
       <c r="B10" t="n">
         <v>90135</v>
@@ -1578,10 +1573,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638021</v>
+        <v>638130</v>
       </c>
       <c r="R10" t="n">
-        <v>7033637</v>
+        <v>7033646</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1644,10 +1639,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113714950</v>
+        <v>113712757</v>
       </c>
       <c r="B11" t="n">
-        <v>78201</v>
+        <v>56029</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1656,25 +1651,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1684,10 +1679,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638039</v>
+        <v>638143</v>
       </c>
       <c r="R11" t="n">
-        <v>7033691</v>
+        <v>7033756</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1724,7 +1719,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Riklig</t>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113714952</v>
+        <v>113714955</v>
       </c>
       <c r="B12" t="n">
-        <v>56029</v>
+        <v>96371</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1795,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638041</v>
+        <v>638085</v>
       </c>
       <c r="R12" t="n">
-        <v>7033714</v>
+        <v>7033772</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1831,11 +1826,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>En tupp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,10 +1856,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113712791</v>
+        <v>113712797</v>
       </c>
       <c r="B13" t="n">
-        <v>90522</v>
+        <v>90135</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,16 +1872,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1901,10 +1896,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638310</v>
+        <v>638110</v>
       </c>
       <c r="R13" t="n">
-        <v>7033687</v>
+        <v>7033643</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1937,11 +1932,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Mycket gammal fruktkropp på gammal granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113714954</v>
+        <v>113712795</v>
       </c>
       <c r="B14" t="n">
-        <v>90577</v>
+        <v>90135</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,25 +1974,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2012,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638088</v>
+        <v>638152</v>
       </c>
       <c r="R14" t="n">
-        <v>7033754</v>
+        <v>7033629</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2078,7 +2068,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113714889</v>
+        <v>113712756</v>
       </c>
       <c r="B15" t="n">
         <v>78201</v>
@@ -2118,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>637971</v>
+        <v>638127</v>
       </c>
       <c r="R15" t="n">
-        <v>7033859</v>
+        <v>7033780</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2148,12 +2138,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2189,10 +2179,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113712792</v>
+        <v>113712683</v>
       </c>
       <c r="B16" t="n">
-        <v>90153</v>
+        <v>78201</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2205,21 +2195,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2229,10 +2219,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>638281</v>
+        <v>637971</v>
       </c>
       <c r="R16" t="n">
-        <v>7033658</v>
+        <v>7033859</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2259,12 +2249,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113712684</v>
+        <v>113712798</v>
       </c>
       <c r="B17" t="n">
-        <v>78794</v>
+        <v>78201</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,21 +2306,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2335,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>637878</v>
+        <v>638106</v>
       </c>
       <c r="R17" t="n">
-        <v>7033847</v>
+        <v>7033670</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2365,12 +2360,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,7 +2396,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113712793</v>
+        <v>113712749</v>
       </c>
       <c r="B18" t="n">
         <v>78201</v>
@@ -2441,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638229</v>
+        <v>638039</v>
       </c>
       <c r="R18" t="n">
-        <v>7033645</v>
+        <v>7033691</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2477,6 +2472,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113712794</v>
+        <v>113712800</v>
       </c>
       <c r="B19" t="n">
-        <v>90596</v>
+        <v>56810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2523,21 +2523,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5467</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638195</v>
+        <v>638031</v>
       </c>
       <c r="R19" t="n">
         <v>7033639</v>
@@ -2583,6 +2583,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2613,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113712798</v>
+        <v>113712802</v>
       </c>
       <c r="B20" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2629,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2653,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>638106</v>
+        <v>638021</v>
       </c>
       <c r="R20" t="n">
-        <v>7033670</v>
+        <v>7033637</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2719,10 +2724,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113712753</v>
+        <v>113712684</v>
       </c>
       <c r="B21" t="n">
-        <v>90135</v>
+        <v>78794</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2735,21 +2740,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2759,10 +2764,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>638082</v>
+        <v>637878</v>
       </c>
       <c r="R21" t="n">
-        <v>7033727</v>
+        <v>7033847</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2789,12 +2794,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2825,7 +2830,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113712756</v>
+        <v>113712793</v>
       </c>
       <c r="B22" t="n">
         <v>78201</v>
@@ -2865,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638127</v>
+        <v>638229</v>
       </c>
       <c r="R22" t="n">
-        <v>7033780</v>
+        <v>7033645</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2901,11 +2906,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2936,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113712799</v>
+        <v>113712794</v>
       </c>
       <c r="B23" t="n">
-        <v>90135</v>
+        <v>90596</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2952,21 +2952,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5467</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>638079</v>
+        <v>638195</v>
       </c>
       <c r="R23" t="n">
-        <v>7033653</v>
+        <v>7033639</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3042,10 +3042,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113714984</v>
+        <v>113712792</v>
       </c>
       <c r="B24" t="n">
-        <v>78794</v>
+        <v>90153</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3058,21 +3058,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>638151</v>
+        <v>638281</v>
       </c>
       <c r="R24" t="n">
-        <v>7033618</v>
+        <v>7033658</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 26079-2020 artfynd.xlsx
+++ b/artfynd/A 26079-2020 artfynd.xlsx
@@ -2290,10 +2290,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113712798</v>
+        <v>113712802</v>
       </c>
       <c r="B17" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,21 +2306,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638106</v>
+        <v>638021</v>
       </c>
       <c r="R17" t="n">
-        <v>7033670</v>
+        <v>7033637</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2396,7 +2396,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113712749</v>
+        <v>113712798</v>
       </c>
       <c r="B18" t="n">
         <v>78201</v>
@@ -2436,10 +2436,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638039</v>
+        <v>638106</v>
       </c>
       <c r="R18" t="n">
-        <v>7033691</v>
+        <v>7033670</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2472,11 +2472,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2507,10 +2502,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113712800</v>
+        <v>113712749</v>
       </c>
       <c r="B19" t="n">
-        <v>56810</v>
+        <v>78201</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2523,21 +2518,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2547,10 +2542,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638031</v>
+        <v>638039</v>
       </c>
       <c r="R19" t="n">
-        <v>7033639</v>
+        <v>7033691</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2587,7 +2582,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2618,10 +2613,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113712802</v>
+        <v>113712800</v>
       </c>
       <c r="B20" t="n">
-        <v>90135</v>
+        <v>56810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,21 +2629,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2658,10 +2653,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>638021</v>
+        <v>638031</v>
       </c>
       <c r="R20" t="n">
-        <v>7033637</v>
+        <v>7033639</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2694,6 +2689,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,7 +2724,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113712684</v>
+        <v>113714890</v>
       </c>
       <c r="B21" t="n">
         <v>78794</v>

--- a/artfynd/A 26079-2020 artfynd.xlsx
+++ b/artfynd/A 26079-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113714984</v>
+        <v>113714955</v>
       </c>
       <c r="B2" t="n">
-        <v>78794</v>
+        <v>96371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>638151</v>
+        <v>638085</v>
       </c>
       <c r="R2" t="n">
-        <v>7033618</v>
+        <v>7033772</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113714954</v>
+        <v>113714952</v>
       </c>
       <c r="B3" t="n">
-        <v>90577</v>
+        <v>56029</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638088</v>
+        <v>638041</v>
       </c>
       <c r="R3" t="n">
-        <v>7033754</v>
+        <v>7033714</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113712753</v>
+        <v>113714951</v>
       </c>
       <c r="B4" t="n">
-        <v>90135</v>
+        <v>56029</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>638082</v>
+        <v>638206</v>
       </c>
       <c r="R4" t="n">
-        <v>7033727</v>
+        <v>7033778</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -963,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>En höna</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113714951</v>
+        <v>113712792</v>
       </c>
       <c r="B5" t="n">
-        <v>56029</v>
+        <v>90153</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>638206</v>
+        <v>638281</v>
       </c>
       <c r="R5" t="n">
-        <v>7033778</v>
+        <v>7033658</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1069,11 +1079,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>En höna</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113712752</v>
+        <v>113712802</v>
       </c>
       <c r="B6" t="n">
-        <v>56029</v>
+        <v>90135</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1116,25 +1121,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>638041</v>
+        <v>638021</v>
       </c>
       <c r="R6" t="n">
-        <v>7033714</v>
+        <v>7033637</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1180,11 +1185,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>En tupp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113712791</v>
+        <v>113712795</v>
       </c>
       <c r="B7" t="n">
-        <v>90522</v>
+        <v>90135</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,16 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>638310</v>
+        <v>638152</v>
       </c>
       <c r="R7" t="n">
-        <v>7033687</v>
+        <v>7033629</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1286,11 +1291,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Mycket gammal fruktkropp på gammal granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113712801</v>
+        <v>113714957</v>
       </c>
       <c r="B8" t="n">
-        <v>90577</v>
+        <v>56029</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1333,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>638021</v>
+        <v>638143</v>
       </c>
       <c r="R8" t="n">
-        <v>7033632</v>
+        <v>7033756</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1397,6 +1397,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>En tupp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113712799</v>
+        <v>113712793</v>
       </c>
       <c r="B9" t="n">
-        <v>90135</v>
+        <v>78201</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1443,21 +1448,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1467,10 +1472,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>638079</v>
+        <v>638229</v>
       </c>
       <c r="R9" t="n">
-        <v>7033653</v>
+        <v>7033645</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1533,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113712796</v>
+        <v>113714890</v>
       </c>
       <c r="B10" t="n">
-        <v>90135</v>
+        <v>78794</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1549,21 +1554,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1573,10 +1578,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>638130</v>
+        <v>637878</v>
       </c>
       <c r="R10" t="n">
-        <v>7033646</v>
+        <v>7033847</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1603,12 +1608,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1639,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113712757</v>
+        <v>113712800</v>
       </c>
       <c r="B11" t="n">
-        <v>56029</v>
+        <v>56810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1651,25 +1656,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1679,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>638143</v>
+        <v>638031</v>
       </c>
       <c r="R11" t="n">
-        <v>7033756</v>
+        <v>7033639</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1719,7 +1724,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>En tupp</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1750,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113714955</v>
+        <v>113714956</v>
       </c>
       <c r="B12" t="n">
-        <v>96371</v>
+        <v>78201</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1762,25 +1767,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1795,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>638085</v>
+        <v>638127</v>
       </c>
       <c r="R12" t="n">
-        <v>7033772</v>
+        <v>7033780</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1826,6 +1831,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1856,10 +1866,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113712797</v>
+        <v>113714950</v>
       </c>
       <c r="B13" t="n">
-        <v>90135</v>
+        <v>78201</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,21 +1882,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1896,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>638110</v>
+        <v>638039</v>
       </c>
       <c r="R13" t="n">
-        <v>7033643</v>
+        <v>7033691</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1932,6 +1942,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-09-24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1962,7 +1977,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113712795</v>
+        <v>113712797</v>
       </c>
       <c r="B14" t="n">
         <v>90135</v>
@@ -2002,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>638152</v>
+        <v>638110</v>
       </c>
       <c r="R14" t="n">
-        <v>7033629</v>
+        <v>7033643</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2068,10 +2083,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113712756</v>
+        <v>113712753</v>
       </c>
       <c r="B15" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2084,21 +2099,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2108,10 +2123,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>638127</v>
+        <v>638082</v>
       </c>
       <c r="R15" t="n">
-        <v>7033780</v>
+        <v>7033727</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2144,11 +2159,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Riklig</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2179,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113712683</v>
+        <v>113712794</v>
       </c>
       <c r="B16" t="n">
-        <v>78201</v>
+        <v>90596</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2195,21 +2205,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5467</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kådvaxskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia serialis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2219,10 +2229,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>637971</v>
+        <v>638195</v>
       </c>
       <c r="R16" t="n">
-        <v>7033859</v>
+        <v>7033639</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2249,17 +2259,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Riklig</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2290,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113712802</v>
+        <v>113712784</v>
       </c>
       <c r="B17" t="n">
-        <v>90135</v>
+        <v>78794</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2306,21 +2311,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2335,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>638021</v>
+        <v>638151</v>
       </c>
       <c r="R17" t="n">
-        <v>7033637</v>
+        <v>7033618</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2396,7 +2401,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113712798</v>
+        <v>113714889</v>
       </c>
       <c r="B18" t="n">
         <v>78201</v>
@@ -2436,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>638106</v>
+        <v>637971</v>
       </c>
       <c r="R18" t="n">
-        <v>7033670</v>
+        <v>7033859</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2466,12 +2471,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2023-09-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,10 +2512,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113712749</v>
+        <v>113712791</v>
       </c>
       <c r="B19" t="n">
-        <v>78201</v>
+        <v>90522</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2518,21 +2528,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2547,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>638039</v>
+        <v>638310</v>
       </c>
       <c r="R19" t="n">
-        <v>7033691</v>
+        <v>7033687</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2582,7 +2587,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Riklig</t>
+          <t>Mycket gammal fruktkropp på gammal granlåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2613,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113712800</v>
+        <v>113712754</v>
       </c>
       <c r="B20" t="n">
-        <v>56810</v>
+        <v>90577</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2625,25 +2630,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2653,10 +2658,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>638031</v>
+        <v>638088</v>
       </c>
       <c r="R20" t="n">
-        <v>7033639</v>
+        <v>7033754</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2689,11 +2694,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2023-09-24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,10 +2724,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113714890</v>
+        <v>113712799</v>
       </c>
       <c r="B21" t="n">
-        <v>78794</v>
+        <v>90135</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>637878</v>
+        <v>638079</v>
       </c>
       <c r="R21" t="n">
-        <v>7033847</v>
+        <v>7033653</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2794,12 +2794,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-27</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113712793</v>
+        <v>113712796</v>
       </c>
       <c r="B22" t="n">
-        <v>78201</v>
+        <v>90135</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2846,21 +2846,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>638229</v>
+        <v>638130</v>
       </c>
       <c r="R22" t="n">
-        <v>7033645</v>
+        <v>7033646</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113712794</v>
+        <v>113712801</v>
       </c>
       <c r="B23" t="n">
-        <v>90596</v>
+        <v>90577</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2948,25 +2948,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5467</v>
+        <v>1209</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kådvaxskinn</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phlebia serialis</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Donk</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2976,10 +2976,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>638195</v>
+        <v>638021</v>
       </c>
       <c r="R23" t="n">
-        <v>7033639</v>
+        <v>7033632</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3042,10 +3042,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>113712792</v>
+        <v>113712798</v>
       </c>
       <c r="B24" t="n">
-        <v>90153</v>
+        <v>78201</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3058,21 +3058,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3082,10 +3082,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>638281</v>
+        <v>638106</v>
       </c>
       <c r="R24" t="n">
-        <v>7033658</v>
+        <v>7033670</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 26079-2020 artfynd.xlsx
+++ b/artfynd/A 26079-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
